--- a/artfynd/A 22380-2024 artfynd.xlsx
+++ b/artfynd/A 22380-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118444231</v>
+        <v>118444237</v>
       </c>
       <c r="B2" t="n">
-        <v>57306</v>
+        <v>78484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>871420</v>
+        <v>871416</v>
       </c>
       <c r="R2" t="n">
-        <v>7443174</v>
+        <v>7443345</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118444228</v>
+        <v>118443444</v>
       </c>
       <c r="B3" t="n">
-        <v>57290</v>
+        <v>57306</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>871409</v>
+        <v>871581</v>
       </c>
       <c r="R3" t="n">
-        <v>7443282</v>
+        <v>7443390</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Avbarkad graa</t>
+          <t>Avbarkad</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,12 +872,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118444237</v>
+        <v>118444231</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>57306</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>871416</v>
+        <v>871420</v>
       </c>
       <c r="R5" t="n">
-        <v>7443345</v>
+        <v>7443174</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1067,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118444239</v>
+        <v>118444228</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>871606</v>
+        <v>871409</v>
       </c>
       <c r="R6" t="n">
-        <v>7443152</v>
+        <v>7443282</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1169,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Avbarkad graa</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118444236</v>
+        <v>118444238</v>
       </c>
       <c r="B7" t="n">
         <v>78484</v>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>871497</v>
+        <v>871387</v>
       </c>
       <c r="R7" t="n">
-        <v>7443343</v>
+        <v>7443321</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1399,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118444238</v>
+        <v>118444239</v>
       </c>
       <c r="B9" t="n">
         <v>78484</v>
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>871387</v>
+        <v>871606</v>
       </c>
       <c r="R9" t="n">
-        <v>7443321</v>
+        <v>7443152</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1501,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118443444</v>
+        <v>118444236</v>
       </c>
       <c r="B10" t="n">
-        <v>57306</v>
+        <v>78484</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>871581</v>
+        <v>871497</v>
       </c>
       <c r="R10" t="n">
-        <v>7443390</v>
+        <v>7443343</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1579,11 +1584,6 @@
           <t>2024-07-14</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Avbarkad</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1596,12 +1596,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 22380-2024 artfynd.xlsx
+++ b/artfynd/A 22380-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118444237</v>
+        <v>118444227</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>90469</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>871416</v>
+        <v>871418</v>
       </c>
       <c r="R2" t="n">
-        <v>7443345</v>
+        <v>7443350</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118443444</v>
+        <v>118444236</v>
       </c>
       <c r="B3" t="n">
-        <v>57306</v>
+        <v>78484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>871581</v>
+        <v>871497</v>
       </c>
       <c r="R3" t="n">
-        <v>7443390</v>
+        <v>7443343</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -855,11 +855,6 @@
           <t>2024-07-14</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Avbarkad</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118444226</v>
+        <v>118444239</v>
       </c>
       <c r="B4" t="n">
-        <v>90666</v>
+        <v>78484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>871403</v>
+        <v>871606</v>
       </c>
       <c r="R4" t="n">
-        <v>7443334</v>
+        <v>7443152</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118444231</v>
+        <v>118444226</v>
       </c>
       <c r="B5" t="n">
-        <v>57306</v>
+        <v>90666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1588</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>871420</v>
+        <v>871403</v>
       </c>
       <c r="R5" t="n">
-        <v>7443174</v>
+        <v>7443334</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1062,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118444228</v>
+        <v>118443444</v>
       </c>
       <c r="B6" t="n">
-        <v>57290</v>
+        <v>57306</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,16 +1099,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1133,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>871409</v>
+        <v>871581</v>
       </c>
       <c r="R6" t="n">
-        <v>7443282</v>
+        <v>7443390</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1173,7 +1163,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Avbarkad graa</t>
+          <t>Avbarkad</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118444238</v>
+        <v>118444228</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>871387</v>
+        <v>871409</v>
       </c>
       <c r="R7" t="n">
-        <v>7443321</v>
+        <v>7443282</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1276,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Avbarkad graa</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118444227</v>
+        <v>118444231</v>
       </c>
       <c r="B8" t="n">
-        <v>90469</v>
+        <v>57306</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>871418</v>
+        <v>871420</v>
       </c>
       <c r="R8" t="n">
-        <v>7443350</v>
+        <v>7443174</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1378,6 +1373,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118444239</v>
+        <v>118444237</v>
       </c>
       <c r="B9" t="n">
         <v>78484</v>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>871606</v>
+        <v>871416</v>
       </c>
       <c r="R9" t="n">
-        <v>7443152</v>
+        <v>7443345</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118444236</v>
+        <v>118444238</v>
       </c>
       <c r="B10" t="n">
         <v>78484</v>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>871497</v>
+        <v>871387</v>
       </c>
       <c r="R10" t="n">
-        <v>7443343</v>
+        <v>7443321</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>

--- a/artfynd/A 22380-2024 artfynd.xlsx
+++ b/artfynd/A 22380-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118444227</v>
+        <v>118444231</v>
       </c>
       <c r="B2" t="n">
-        <v>90469</v>
+        <v>57306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>871418</v>
+        <v>871420</v>
       </c>
       <c r="R2" t="n">
-        <v>7443350</v>
+        <v>7443174</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118444236</v>
+        <v>118444227</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>90476</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>871497</v>
+        <v>871418</v>
       </c>
       <c r="R3" t="n">
-        <v>7443343</v>
+        <v>7443350</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118444239</v>
+        <v>118444228</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>871606</v>
+        <v>871409</v>
       </c>
       <c r="R4" t="n">
-        <v>7443152</v>
+        <v>7443282</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -955,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Avbarkad graa</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118444226</v>
+        <v>118443444</v>
       </c>
       <c r="B5" t="n">
-        <v>90666</v>
+        <v>57306</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1588</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>871403</v>
+        <v>871581</v>
       </c>
       <c r="R5" t="n">
-        <v>7443334</v>
+        <v>7443390</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1059,6 +1069,11 @@
           <t>2024-07-14</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Avbarkad</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1071,22 +1086,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118443444</v>
+        <v>118444239</v>
       </c>
       <c r="B6" t="n">
-        <v>57306</v>
+        <v>78491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>871581</v>
+        <v>871606</v>
       </c>
       <c r="R6" t="n">
-        <v>7443390</v>
+        <v>7443152</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1161,11 +1176,6 @@
           <t>2024-07-14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Avbarkad</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1178,22 +1188,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118444228</v>
+        <v>118444226</v>
       </c>
       <c r="B7" t="n">
-        <v>57290</v>
+        <v>90673</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>871409</v>
+        <v>871403</v>
       </c>
       <c r="R7" t="n">
-        <v>7443282</v>
+        <v>7443334</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1266,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Avbarkad graa</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118444231</v>
+        <v>118444238</v>
       </c>
       <c r="B8" t="n">
-        <v>57306</v>
+        <v>78491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>871420</v>
+        <v>871387</v>
       </c>
       <c r="R8" t="n">
-        <v>7443174</v>
+        <v>7443321</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1373,11 +1378,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,7 +1407,7 @@
         <v>118444237</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118444238</v>
+        <v>118444236</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>871387</v>
+        <v>871497</v>
       </c>
       <c r="R10" t="n">
-        <v>7443321</v>
+        <v>7443343</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>

--- a/artfynd/A 22380-2024 artfynd.xlsx
+++ b/artfynd/A 22380-2024 artfynd.xlsx
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118444239</v>
+        <v>118444226</v>
       </c>
       <c r="B6" t="n">
-        <v>78491</v>
+        <v>90673</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>871606</v>
+        <v>871403</v>
       </c>
       <c r="R6" t="n">
-        <v>7443152</v>
+        <v>7443334</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118444226</v>
+        <v>118444239</v>
       </c>
       <c r="B7" t="n">
-        <v>90673</v>
+        <v>78491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>871403</v>
+        <v>871606</v>
       </c>
       <c r="R7" t="n">
-        <v>7443334</v>
+        <v>7443152</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>

--- a/artfynd/A 22380-2024 artfynd.xlsx
+++ b/artfynd/A 22380-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118444231</v>
+        <v>118443444</v>
       </c>
       <c r="B2" t="n">
         <v>57306</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>871420</v>
+        <v>871581</v>
       </c>
       <c r="R2" t="n">
-        <v>7443174</v>
+        <v>7443390</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Avbarkad tall</t>
+          <t>Avbarkad</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118444227</v>
+        <v>118444228</v>
       </c>
       <c r="B3" t="n">
-        <v>90476</v>
+        <v>57290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>871418</v>
+        <v>871409</v>
       </c>
       <c r="R3" t="n">
-        <v>7443350</v>
+        <v>7443282</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Avbarkad graa</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118444228</v>
+        <v>118444227</v>
       </c>
       <c r="B4" t="n">
-        <v>57290</v>
+        <v>90476</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>871409</v>
+        <v>871418</v>
       </c>
       <c r="R4" t="n">
-        <v>7443282</v>
+        <v>7443350</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Avbarkad graa</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118443444</v>
+        <v>118444231</v>
       </c>
       <c r="B5" t="n">
         <v>57306</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>871581</v>
+        <v>871420</v>
       </c>
       <c r="R5" t="n">
-        <v>7443390</v>
+        <v>7443174</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Avbarkad</t>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,22 +1086,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118444226</v>
+        <v>118444238</v>
       </c>
       <c r="B6" t="n">
-        <v>90673</v>
+        <v>78491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>871403</v>
+        <v>871387</v>
       </c>
       <c r="R6" t="n">
-        <v>7443334</v>
+        <v>7443321</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118444239</v>
+        <v>118444236</v>
       </c>
       <c r="B7" t="n">
         <v>78491</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>871606</v>
+        <v>871497</v>
       </c>
       <c r="R7" t="n">
-        <v>7443152</v>
+        <v>7443343</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118444238</v>
+        <v>118444237</v>
       </c>
       <c r="B8" t="n">
         <v>78491</v>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>871387</v>
+        <v>871416</v>
       </c>
       <c r="R8" t="n">
-        <v>7443321</v>
+        <v>7443345</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118444237</v>
+        <v>118444226</v>
       </c>
       <c r="B9" t="n">
-        <v>78491</v>
+        <v>90673</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>871416</v>
+        <v>871403</v>
       </c>
       <c r="R9" t="n">
-        <v>7443345</v>
+        <v>7443334</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118444236</v>
+        <v>118444239</v>
       </c>
       <c r="B10" t="n">
         <v>78491</v>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>871497</v>
+        <v>871606</v>
       </c>
       <c r="R10" t="n">
-        <v>7443343</v>
+        <v>7443152</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>

--- a/artfynd/A 22380-2024 artfynd.xlsx
+++ b/artfynd/A 22380-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118444228</v>
+        <v>118444226</v>
       </c>
       <c r="B2" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>871409</v>
+        <v>871403</v>
       </c>
       <c r="R2" t="n">
-        <v>7443282</v>
+        <v>7443334</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Avbarkad graa</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118443444</v>
+        <v>118444227</v>
       </c>
       <c r="B3" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>871581</v>
+        <v>871418</v>
       </c>
       <c r="R3" t="n">
-        <v>7443390</v>
+        <v>7443350</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -860,11 +845,6 @@
           <t>2024-07-14</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Avbarkad</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -877,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -892,16 +872,11 @@
         <v>118444236</v>
       </c>
       <c r="B4" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -994,16 +969,11 @@
         <v>118444237</v>
       </c>
       <c r="B5" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1093,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118444227</v>
+        <v>118444238</v>
       </c>
       <c r="B6" t="n">
-        <v>90478</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>871418</v>
+        <v>871387</v>
       </c>
       <c r="R6" t="n">
-        <v>7443350</v>
+        <v>7443321</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1195,19 +1160,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118444238</v>
+        <v>118444239</v>
       </c>
       <c r="B7" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1235,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>871387</v>
+        <v>871606</v>
       </c>
       <c r="R7" t="n">
-        <v>7443321</v>
+        <v>7443152</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1297,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118444239</v>
+        <v>118443444</v>
       </c>
       <c r="B8" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>871606</v>
+        <v>871581</v>
       </c>
       <c r="R8" t="n">
-        <v>7443152</v>
+        <v>7443390</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1375,6 +1330,11 @@
           <t>2024-07-14</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Avbarkad</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1387,49 +1347,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118444226</v>
+        <v>118444231</v>
       </c>
       <c r="B9" t="n">
-        <v>90675</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1588</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>871403</v>
+        <v>871420</v>
       </c>
       <c r="R9" t="n">
-        <v>7443334</v>
+        <v>7443174</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1475,6 +1430,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,15 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118444231</v>
+        <v>118444228</v>
       </c>
       <c r="B10" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1517,16 +1472,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1541,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>871420</v>
+        <v>871409</v>
       </c>
       <c r="R10" t="n">
-        <v>7443174</v>
+        <v>7443282</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1581,7 +1536,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Avbarkad tall</t>
+          <t>Avbarkad graa</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 22380-2024 artfynd.xlsx
+++ b/artfynd/A 22380-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118444226</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118444227</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118444236</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118444237</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118444238</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118444239</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118443444</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118444231</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,8 +1605,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118444228</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>